--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ31"/>
+  <dimension ref="A1:AZ28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1770,7 +1770,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136993667</v>
+        <v>136993698</v>
       </c>
       <c r="B12" t="n">
         <v>79476</v>
@@ -1800,7 +1800,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579385</v>
+        <v>579448</v>
       </c>
       <c r="R12" t="n">
-        <v>6336585</v>
+        <v>6336507</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1874,13 +1874,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993667</t>
+          <t>https://artportalen.se/Sighting/136993698</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136993698</v>
+        <v>136993740</v>
       </c>
       <c r="B13" t="n">
         <v>79476</v>
@@ -1910,7 +1910,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1922,10 +1922,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579448</v>
+        <v>579458</v>
       </c>
       <c r="R13" t="n">
-        <v>6336507</v>
+        <v>6336501</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1984,16 +1984,16 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993698</t>
+          <t>https://artportalen.se/Sighting/136993740</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136993740</v>
+        <v>136983277</v>
       </c>
       <c r="B14" t="n">
-        <v>79476</v>
+        <v>99353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2001,44 +2001,51 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>mönsterås, Sm</t>
+          <t>Horvan, Horvan, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579458</v>
+        <v>579186</v>
       </c>
       <c r="R14" t="n">
-        <v>6336501</v>
+        <v>6336608</v>
       </c>
       <c r="S14" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2076,34 +2083,33 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993740</t>
+          <t>https://artportalen.se/Sighting/136983277</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136993757</v>
+        <v>136983311</v>
       </c>
       <c r="B15" t="n">
-        <v>79476</v>
+        <v>99353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2111,44 +2117,51 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>mönsterås, Sm</t>
+          <t>Horvan, Horvan, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579433</v>
+        <v>579177</v>
       </c>
       <c r="R15" t="n">
-        <v>6336481</v>
+        <v>6336619</v>
       </c>
       <c r="S15" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2186,34 +2199,33 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993757</t>
+          <t>https://artportalen.se/Sighting/136983311</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136993819</v>
+        <v>136983411</v>
       </c>
       <c r="B16" t="n">
-        <v>79476</v>
+        <v>99353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2221,44 +2233,51 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>mönsterås, Sm</t>
+          <t>Horvan, Horvan, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579402</v>
+        <v>579205</v>
       </c>
       <c r="R16" t="n">
-        <v>6336515</v>
+        <v>6336680</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2296,31 +2315,30 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993819</t>
+          <t>https://artportalen.se/Sighting/136983411</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136983277</v>
+        <v>136983686</v>
       </c>
       <c r="B17" t="n">
         <v>99353</v>
@@ -2350,12 +2368,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2369,13 +2387,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579186</v>
+        <v>579197</v>
       </c>
       <c r="R17" t="n">
-        <v>6336608</v>
+        <v>6336710</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2430,13 +2448,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136983277</t>
+          <t>https://artportalen.se/Sighting/136983686</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136983311</v>
+        <v>136984362</v>
       </c>
       <c r="B18" t="n">
         <v>99353</v>
@@ -2466,17 +2484,17 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2485,13 +2503,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579177</v>
+        <v>579226</v>
       </c>
       <c r="R18" t="n">
-        <v>6336619</v>
+        <v>6336679</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2546,13 +2564,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136983311</t>
+          <t>https://artportalen.se/Sighting/136984362</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136983411</v>
+        <v>136984465</v>
       </c>
       <c r="B19" t="n">
         <v>99353</v>
@@ -2582,7 +2600,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2601,13 +2619,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579205</v>
+        <v>579207</v>
       </c>
       <c r="R19" t="n">
-        <v>6336680</v>
+        <v>6336640</v>
       </c>
       <c r="S19" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2662,13 +2680,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136983411</t>
+          <t>https://artportalen.se/Sighting/136984465</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136983686</v>
+        <v>136984524</v>
       </c>
       <c r="B20" t="n">
         <v>99353</v>
@@ -2698,7 +2716,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2717,13 +2735,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579197</v>
+        <v>579216</v>
       </c>
       <c r="R20" t="n">
-        <v>6336710</v>
+        <v>6336629</v>
       </c>
       <c r="S20" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2778,13 +2796,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136983686</t>
+          <t>https://artportalen.se/Sighting/136984524</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136984362</v>
+        <v>136984621</v>
       </c>
       <c r="B21" t="n">
         <v>99353</v>
@@ -2814,12 +2832,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2833,13 +2851,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>579226</v>
+        <v>579238</v>
       </c>
       <c r="R21" t="n">
-        <v>6336679</v>
+        <v>6336576</v>
       </c>
       <c r="S21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2894,13 +2912,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136984362</t>
+          <t>https://artportalen.se/Sighting/136984621</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136984465</v>
+        <v>136984780</v>
       </c>
       <c r="B22" t="n">
         <v>99353</v>
@@ -2930,7 +2948,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2949,13 +2967,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579207</v>
+        <v>579229</v>
       </c>
       <c r="R22" t="n">
-        <v>6336640</v>
+        <v>6336554</v>
       </c>
       <c r="S22" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3010,13 +3028,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136984465</t>
+          <t>https://artportalen.se/Sighting/136984780</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136984524</v>
+        <v>136986187</v>
       </c>
       <c r="B23" t="n">
         <v>99353</v>
@@ -3046,12 +3064,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3065,13 +3078,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>579216</v>
+        <v>579345</v>
       </c>
       <c r="R23" t="n">
-        <v>6336629</v>
+        <v>6336499</v>
       </c>
       <c r="S23" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3126,13 +3139,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136984524</t>
+          <t>https://artportalen.se/Sighting/136986187</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136984621</v>
+        <v>136988419</v>
       </c>
       <c r="B24" t="n">
         <v>99353</v>
@@ -3162,17 +3175,17 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3181,13 +3194,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>579238</v>
+        <v>579285</v>
       </c>
       <c r="R24" t="n">
-        <v>6336576</v>
+        <v>6336609</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3242,13 +3255,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136984621</t>
+          <t>https://artportalen.se/Sighting/136988419</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136984780</v>
+        <v>136988674</v>
       </c>
       <c r="B25" t="n">
         <v>99353</v>
@@ -3278,7 +3291,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3288,7 +3301,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3297,13 +3310,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>579229</v>
+        <v>579278</v>
       </c>
       <c r="R25" t="n">
-        <v>6336554</v>
+        <v>6336579</v>
       </c>
       <c r="S25" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3358,13 +3371,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136984780</t>
+          <t>https://artportalen.se/Sighting/136988674</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136986187</v>
+        <v>136993796</v>
       </c>
       <c r="B26" t="n">
         <v>99353</v>
@@ -3394,27 +3407,26 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Horvan, Horvan, Sm</t>
+          <t>mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>579345</v>
+        <v>579433</v>
       </c>
       <c r="R26" t="n">
-        <v>6336499</v>
+        <v>6336481</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3452,85 +3464,80 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136986187</t>
+          <t>https://artportalen.se/Sighting/136993796</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136988419</v>
+        <v>136993906</v>
       </c>
       <c r="B27" t="n">
-        <v>99353</v>
+        <v>106494</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Horvan, Horvan, Sm</t>
+          <t>MÖNSTERÅS, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>579285</v>
+        <v>579189</v>
       </c>
       <c r="R27" t="n">
-        <v>6336609</v>
+        <v>6336730</v>
       </c>
       <c r="S27" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3568,85 +3575,80 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136988419</t>
+          <t>https://artportalen.se/Sighting/136993906</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136988674</v>
+        <v>136993294</v>
       </c>
       <c r="B28" t="n">
-        <v>99353</v>
+        <v>98215</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Horvan, Horvan, Sm</t>
+          <t>mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>579278</v>
+        <v>579349</v>
       </c>
       <c r="R28" t="n">
-        <v>6336579</v>
+        <v>6336590</v>
       </c>
       <c r="S28" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3684,355 +3686,23 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136988674</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>136993796</v>
-      </c>
-      <c r="B29" t="n">
-        <v>99353</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>mönsterås, Sm</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>579433</v>
-      </c>
-      <c r="R29" t="n">
-        <v>6336481</v>
-      </c>
-      <c r="S29" t="n">
-        <v>1</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Fliseryd</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF29" t="inlineStr"/>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Gunilla Rosendahl</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Gunilla Rosendahl</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136993796</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>136993906</v>
-      </c>
-      <c r="B30" t="n">
-        <v>106494</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>MÖNSTERÅS, Sm</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>579189</v>
-      </c>
-      <c r="R30" t="n">
-        <v>6336730</v>
-      </c>
-      <c r="S30" t="n">
-        <v>1</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Fliseryd</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Gunilla Rosendahl</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Gunilla Rosendahl</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136993906</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>136993294</v>
-      </c>
-      <c r="B31" t="n">
-        <v>98215</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>mönsterås, Sm</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>579349</v>
-      </c>
-      <c r="R31" t="n">
-        <v>6336590</v>
-      </c>
-      <c r="S31" t="n">
-        <v>1</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Fliseryd</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF31" t="inlineStr"/>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Gunilla Rosendahl</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Gunilla Rosendahl</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-      <c r="AZ31" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136993294</t>
         </is>
@@ -4067,9 +3737,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136988037</v>
       </c>
       <c r="B2" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136988735</v>
       </c>
       <c r="B3" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>136993560</v>
       </c>
       <c r="B4" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>136993864</v>
       </c>
       <c r="B5" t="n">
-        <v>96938</v>
+        <v>96944</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136985036</v>
       </c>
       <c r="B6" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136993200</v>
       </c>
       <c r="B7" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1330,7 +1330,7 @@
         <v>136993642</v>
       </c>
       <c r="B8" t="n">
-        <v>92134</v>
+        <v>92136</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1440,7 +1440,7 @@
         <v>136987247</v>
       </c>
       <c r="B9" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>136986828</v>
       </c>
       <c r="B10" t="n">
-        <v>92791</v>
+        <v>92793</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1662,7 +1662,7 @@
         <v>136988310</v>
       </c>
       <c r="B11" t="n">
-        <v>92791</v>
+        <v>92793</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>136993698</v>
       </c>
       <c r="B12" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1883,7 +1883,7 @@
         <v>136993740</v>
       </c>
       <c r="B13" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1993,7 +1993,7 @@
         <v>136983277</v>
       </c>
       <c r="B14" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>136983311</v>
       </c>
       <c r="B15" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2225,7 +2225,7 @@
         <v>136983411</v>
       </c>
       <c r="B16" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>136983686</v>
       </c>
       <c r="B17" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2457,7 +2457,7 @@
         <v>136984362</v>
       </c>
       <c r="B18" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>136984465</v>
       </c>
       <c r="B19" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2689,7 +2689,7 @@
         <v>136984524</v>
       </c>
       <c r="B20" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2805,7 +2805,7 @@
         <v>136984621</v>
       </c>
       <c r="B21" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2921,7 +2921,7 @@
         <v>136984780</v>
       </c>
       <c r="B22" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>136986187</v>
       </c>
       <c r="B23" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>136988419</v>
       </c>
       <c r="B24" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>136988674</v>
       </c>
       <c r="B25" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>136993796</v>
       </c>
       <c r="B26" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>136993906</v>
       </c>
       <c r="B27" t="n">
-        <v>106494</v>
+        <v>106500</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>136993294</v>
       </c>
       <c r="B28" t="n">
-        <v>98215</v>
+        <v>98221</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>

--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ28"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,48 +680,57 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>136988037</v>
+        <v>137059663</v>
       </c>
       <c r="B2" t="n">
-        <v>96944</v>
+        <v>92753</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>1101</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Horvan, Horvan, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>579362</v>
+        <v>579385</v>
       </c>
       <c r="R2" t="n">
-        <v>6336597</v>
+        <v>6336525</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +754,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,54 +785,63 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136988037</t>
+          <t>https://artportalen.se/Sighting/137059663</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>136988735</v>
+        <v>137062062</v>
       </c>
       <c r="B3" t="n">
-        <v>96944</v>
+        <v>92753</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>1101</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Gropticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Postia guttulata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(Peck) Jülich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Horvan, Horvan, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>579293</v>
+        <v>579351</v>
       </c>
       <c r="R3" t="n">
-        <v>6336540</v>
+        <v>6336507</v>
       </c>
       <c r="S3" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -847,12 +865,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,16 +896,16 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136988735</t>
+          <t>https://artportalen.se/Sighting/137062062</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>136993560</v>
+        <v>136988037</v>
       </c>
       <c r="B4" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,28 +930,20 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>mönsterås, Sm</t>
+          <t>Horvan, Horvan, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>579347</v>
+        <v>579362</v>
       </c>
       <c r="R4" t="n">
-        <v>6336573</v>
+        <v>6336597</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -971,34 +981,33 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993560</t>
+          <t>https://artportalen.se/Sighting/136988037</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>136993864</v>
+        <v>136988735</v>
       </c>
       <c r="B5" t="n">
-        <v>96944</v>
+        <v>96946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1023,28 +1032,20 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>MÖNSTERÅS, Sm</t>
+          <t>Horvan, Horvan, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>579332</v>
+        <v>579293</v>
       </c>
       <c r="R5" t="n">
-        <v>6336521</v>
+        <v>6336540</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,56 +1083,55 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993864</t>
+          <t>https://artportalen.se/Sighting/136988735</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>136985036</v>
+        <v>136993560</v>
       </c>
       <c r="B6" t="n">
-        <v>92136</v>
+        <v>96946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1139,24 +1139,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Horvan, Horvan, Sm</t>
+          <t>mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>579195</v>
+        <v>579347</v>
       </c>
       <c r="R6" t="n">
-        <v>6336527</v>
+        <v>6336573</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,75 +1193,77 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136985036</t>
+          <t>https://artportalen.se/Sighting/136993560</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>136993200</v>
+        <v>136993864</v>
       </c>
       <c r="B7" t="n">
-        <v>92136</v>
+        <v>96946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Mönsterås, Sm</t>
+          <t>MÖNSTERÅS, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>579300</v>
+        <v>579332</v>
       </c>
       <c r="R7" t="n">
-        <v>6336590</v>
+        <v>6336521</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1321,61 +1322,54 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993200</t>
+          <t>https://artportalen.se/Sighting/136993864</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>136993642</v>
+        <v>137058412</v>
       </c>
       <c r="B8" t="n">
-        <v>92136</v>
+        <v>96946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>mönsterås, Sm</t>
+          <t>Horvan, Horvan, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>579355</v>
+        <v>579364</v>
       </c>
       <c r="R8" t="n">
-        <v>6336544</v>
+        <v>6336538</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1399,12 +1393,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1413,81 +1407,71 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993642</t>
+          <t>https://artportalen.se/Sighting/137058412</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>136987247</v>
+        <v>137060105</v>
       </c>
       <c r="B9" t="n">
-        <v>93451</v>
+        <v>96946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Horvan, Horvan, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>579441</v>
+        <v>579394</v>
       </c>
       <c r="R9" t="n">
-        <v>6336504</v>
+        <v>6336497</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1511,12 +1495,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1542,16 +1526,16 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136987247</t>
+          <t>https://artportalen.se/Sighting/137060105</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>136986828</v>
+        <v>137060188</v>
       </c>
       <c r="B10" t="n">
-        <v>92793</v>
+        <v>96946</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1559,31 +1543,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6031</v>
+        <v>2180</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1592,10 +1576,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>579439</v>
+        <v>579406</v>
       </c>
       <c r="R10" t="n">
-        <v>6336472</v>
+        <v>6336470</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
@@ -1622,12 +1606,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1653,43 +1637,43 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136986828</t>
+          <t>https://artportalen.se/Sighting/137060188</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>136988310</v>
+        <v>136985036</v>
       </c>
       <c r="B11" t="n">
-        <v>92793</v>
+        <v>92138</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6031</v>
+        <v>5442</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1703,13 +1687,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>579363</v>
+        <v>579195</v>
       </c>
       <c r="R11" t="n">
-        <v>6336551</v>
+        <v>6336527</v>
       </c>
       <c r="S11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1764,43 +1748,43 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136988310</t>
+          <t>https://artportalen.se/Sighting/136985036</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>136993698</v>
+        <v>136993200</v>
       </c>
       <c r="B12" t="n">
-        <v>79480</v>
+        <v>92138</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1808,14 +1792,14 @@
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>mönsterås, Sm</t>
+          <t>Mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>579448</v>
+        <v>579300</v>
       </c>
       <c r="R12" t="n">
-        <v>6336507</v>
+        <v>6336590</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1874,43 +1858,43 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993698</t>
+          <t>https://artportalen.se/Sighting/136993200</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>136993740</v>
+        <v>136993642</v>
       </c>
       <c r="B13" t="n">
-        <v>79480</v>
+        <v>92138</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr"/>
@@ -1922,10 +1906,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>579458</v>
+        <v>579355</v>
       </c>
       <c r="R13" t="n">
-        <v>6336501</v>
+        <v>6336544</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -1984,53 +1968,48 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993740</t>
+          <t>https://artportalen.se/Sighting/136993642</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>136983277</v>
+        <v>137059377</v>
       </c>
       <c r="B14" t="n">
-        <v>99359</v>
+        <v>92138</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2039,13 +2018,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>579186</v>
+        <v>579391</v>
       </c>
       <c r="R14" t="n">
-        <v>6336608</v>
+        <v>6336570</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2069,12 +2048,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2100,53 +2079,48 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136983277</t>
+          <t>https://artportalen.se/Sighting/137059377</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>136983311</v>
+        <v>136987247</v>
       </c>
       <c r="B15" t="n">
-        <v>99359</v>
+        <v>93453</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
@@ -2155,10 +2129,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>579177</v>
+        <v>579441</v>
       </c>
       <c r="R15" t="n">
-        <v>6336619</v>
+        <v>6336504</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2216,53 +2190,43 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136983311</t>
+          <t>https://artportalen.se/Sighting/136987247</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>136983411</v>
+        <v>137060719</v>
       </c>
       <c r="B16" t="n">
-        <v>99359</v>
+        <v>93453</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>5966</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2271,13 +2235,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>579205</v>
+        <v>579411</v>
       </c>
       <c r="R16" t="n">
-        <v>6336680</v>
+        <v>6336448</v>
       </c>
       <c r="S16" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2301,12 +2265,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2332,53 +2296,48 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136983411</t>
+          <t>https://artportalen.se/Sighting/137060719</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>136983686</v>
+        <v>136986828</v>
       </c>
       <c r="B17" t="n">
-        <v>99359</v>
+        <v>92795</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2387,10 +2346,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>579197</v>
+        <v>579439</v>
       </c>
       <c r="R17" t="n">
-        <v>6336710</v>
+        <v>6336472</v>
       </c>
       <c r="S17" t="n">
         <v>4</v>
@@ -2448,53 +2407,48 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136983686</t>
+          <t>https://artportalen.se/Sighting/136986828</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>136984362</v>
+        <v>136988310</v>
       </c>
       <c r="B18" t="n">
-        <v>99359</v>
+        <v>92795</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6031</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2503,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>579226</v>
+        <v>579363</v>
       </c>
       <c r="R18" t="n">
-        <v>6336679</v>
+        <v>6336551</v>
       </c>
       <c r="S18" t="n">
         <v>4</v>
@@ -2564,16 +2518,16 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136984362</t>
+          <t>https://artportalen.se/Sighting/136988310</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136984465</v>
+        <v>136993698</v>
       </c>
       <c r="B19" t="n">
-        <v>99359</v>
+        <v>79482</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2581,51 +2535,44 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Horvan, Horvan, Sm</t>
+          <t>mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579207</v>
+        <v>579448</v>
       </c>
       <c r="R19" t="n">
-        <v>6336640</v>
+        <v>6336507</v>
       </c>
       <c r="S19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2663,33 +2610,34 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136984465</t>
+          <t>https://artportalen.se/Sighting/136993698</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136984524</v>
+        <v>136993740</v>
       </c>
       <c r="B20" t="n">
-        <v>99359</v>
+        <v>79482</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2697,51 +2645,44 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Horvan, Horvan, Sm</t>
+          <t>mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579216</v>
+        <v>579458</v>
       </c>
       <c r="R20" t="n">
-        <v>6336629</v>
+        <v>6336501</v>
       </c>
       <c r="S20" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2779,70 +2720,66 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136984524</t>
+          <t>https://artportalen.se/Sighting/136993740</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>136984621</v>
+        <v>137058966</v>
       </c>
       <c r="B21" t="n">
-        <v>99359</v>
+        <v>58005</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>överblommad</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2851,13 +2788,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>579238</v>
+        <v>579383</v>
       </c>
       <c r="R21" t="n">
-        <v>6336576</v>
+        <v>6336606</v>
       </c>
       <c r="S21" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2881,12 +2818,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2912,68 +2849,54 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136984621</t>
+          <t>https://artportalen.se/Sighting/137058966</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>136984780</v>
+        <v>137058799</v>
       </c>
       <c r="B22" t="n">
-        <v>99359</v>
+        <v>58164</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>103023</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Horvan, Horvan, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579229</v>
+        <v>579383</v>
       </c>
       <c r="R22" t="n">
-        <v>6336554</v>
+        <v>6336606</v>
       </c>
       <c r="S22" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2997,12 +2920,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3028,16 +2951,16 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136984780</t>
+          <t>https://artportalen.se/Sighting/137058799</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136986187</v>
+        <v>136983277</v>
       </c>
       <c r="B23" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3064,7 +2987,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3078,13 +3006,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>579345</v>
+        <v>579186</v>
       </c>
       <c r="R23" t="n">
-        <v>6336499</v>
+        <v>6336608</v>
       </c>
       <c r="S23" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3139,16 +3067,16 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136986187</t>
+          <t>https://artportalen.se/Sighting/136983277</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136988419</v>
+        <v>136983311</v>
       </c>
       <c r="B24" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3175,12 +3103,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>45</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3194,13 +3122,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>579285</v>
+        <v>579177</v>
       </c>
       <c r="R24" t="n">
-        <v>6336609</v>
+        <v>6336619</v>
       </c>
       <c r="S24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3255,16 +3183,16 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136988419</t>
+          <t>https://artportalen.se/Sighting/136983311</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136988674</v>
+        <v>136983411</v>
       </c>
       <c r="B25" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3291,7 +3219,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3301,7 +3229,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3310,13 +3238,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>579278</v>
+        <v>579205</v>
       </c>
       <c r="R25" t="n">
-        <v>6336579</v>
+        <v>6336680</v>
       </c>
       <c r="S25" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3371,16 +3299,16 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136988674</t>
+          <t>https://artportalen.se/Sighting/136983411</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136993796</v>
+        <v>136983686</v>
       </c>
       <c r="B26" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3407,26 +3335,32 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>mönsterås, Sm</t>
+          <t>Horvan, Horvan, Sm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>579433</v>
+        <v>579197</v>
       </c>
       <c r="R26" t="n">
-        <v>6336481</v>
+        <v>6336710</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3464,80 +3398,85 @@
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993796</t>
+          <t>https://artportalen.se/Sighting/136983686</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136993906</v>
+        <v>136984362</v>
       </c>
       <c r="B27" t="n">
-        <v>106500</v>
+        <v>99361</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>MÖNSTERÅS, Sm</t>
+          <t>Horvan, Horvan, Sm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>579189</v>
+        <v>579226</v>
       </c>
       <c r="R27" t="n">
-        <v>6336730</v>
+        <v>6336679</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3575,80 +3514,85 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993906</t>
+          <t>https://artportalen.se/Sighting/136984362</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136993294</v>
+        <v>136984465</v>
       </c>
       <c r="B28" t="n">
-        <v>98221</v>
+        <v>99361</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>mönsterås, Sm</t>
+          <t>Horvan, Horvan, Sm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>579349</v>
+        <v>579207</v>
       </c>
       <c r="R28" t="n">
-        <v>6336590</v>
+        <v>6336640</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3686,23 +3630,1046 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136984465</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>136984524</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Horvan, Horvan, Sm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>579216</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6336629</v>
+      </c>
+      <c r="S29" t="n">
+        <v>8</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136984524</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>136984621</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Horvan, Horvan, Sm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>579238</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6336576</v>
+      </c>
+      <c r="S30" t="n">
+        <v>5</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136984621</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>136984780</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Horvan, Horvan, Sm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>579229</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6336554</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136984780</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>136986187</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Horvan, Horvan, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>579345</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6336499</v>
+      </c>
+      <c r="S32" t="n">
+        <v>4</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136986187</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>136988419</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Horvan, Horvan, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>579285</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6336609</v>
+      </c>
+      <c r="S33" t="n">
+        <v>7</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136988419</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>136988674</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>överblommad</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Horvan, Horvan, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>579278</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6336579</v>
+      </c>
+      <c r="S34" t="n">
+        <v>6</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Lars Engström</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136988674</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>136993796</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99361</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>579433</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6336481</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136993796</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>136993906</v>
+      </c>
+      <c r="B36" t="n">
+        <v>106502</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>MÖNSTERÅS, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>579189</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6336730</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136993906</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>136993294</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98223</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>mönsterås, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>579349</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6336590</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Mönsterås</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Fliseryd</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Gunilla Rosendahl</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136993294</t>
         </is>
@@ -3737,6 +4704,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ37"/>
+  <dimension ref="A1:AZ35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2524,55 +2524,57 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>136993698</v>
+        <v>137058966</v>
       </c>
       <c r="B19" t="n">
-        <v>79482</v>
+        <v>58005</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>mönsterås, Sm</t>
+          <t>Horvan, Horvan, Sm</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>579448</v>
+        <v>579383</v>
       </c>
       <c r="R19" t="n">
-        <v>6336507</v>
+        <v>6336606</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2596,12 +2598,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2610,79 +2612,71 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993698</t>
+          <t>https://artportalen.se/Sighting/137058966</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>136993740</v>
+        <v>137058799</v>
       </c>
       <c r="B20" t="n">
-        <v>79482</v>
+        <v>58164</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6425</v>
+        <v>103023</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>mönsterås, Sm</t>
+          <t>Horvan, Horvan, Sm</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>579458</v>
+        <v>579383</v>
       </c>
       <c r="R20" t="n">
-        <v>6336501</v>
+        <v>6336606</v>
       </c>
       <c r="S20" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2706,12 +2700,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2720,66 +2714,70 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Gunilla Rosendahl</t>
+          <t>Lars Engström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136993740</t>
+          <t>https://artportalen.se/Sighting/137058799</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>137058966</v>
+        <v>136983277</v>
       </c>
       <c r="B21" t="n">
-        <v>58005</v>
+        <v>99361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
@@ -2788,13 +2786,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>579383</v>
+        <v>579186</v>
       </c>
       <c r="R21" t="n">
-        <v>6336606</v>
+        <v>6336608</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2818,12 +2816,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2849,54 +2847,68 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137058966</t>
+          <t>https://artportalen.se/Sighting/136983277</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>137058799</v>
+        <v>136983311</v>
       </c>
       <c r="B22" t="n">
-        <v>58164</v>
+        <v>99361</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>103023</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tofsmes</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lophophanes cristatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
           <t>Horvan, Horvan, Sm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>579383</v>
+        <v>579177</v>
       </c>
       <c r="R22" t="n">
-        <v>6336606</v>
+        <v>6336619</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2920,12 +2932,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2026-10-04</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2951,13 +2963,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/137058799</t>
+          <t>https://artportalen.se/Sighting/136983311</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>136983277</v>
+        <v>136983411</v>
       </c>
       <c r="B23" t="n">
         <v>99361</v>
@@ -2987,12 +2999,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -3006,13 +3018,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>579186</v>
+        <v>579205</v>
       </c>
       <c r="R23" t="n">
-        <v>6336608</v>
+        <v>6336680</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3067,13 +3079,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136983277</t>
+          <t>https://artportalen.se/Sighting/136983411</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>136983311</v>
+        <v>136983686</v>
       </c>
       <c r="B24" t="n">
         <v>99361</v>
@@ -3108,7 +3120,7 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3122,13 +3134,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>579177</v>
+        <v>579197</v>
       </c>
       <c r="R24" t="n">
-        <v>6336619</v>
+        <v>6336710</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3183,13 +3195,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136983311</t>
+          <t>https://artportalen.se/Sighting/136983686</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>136983411</v>
+        <v>136984362</v>
       </c>
       <c r="B25" t="n">
         <v>99361</v>
@@ -3219,7 +3231,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -3229,7 +3241,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3238,10 +3250,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>579205</v>
+        <v>579226</v>
       </c>
       <c r="R25" t="n">
-        <v>6336680</v>
+        <v>6336679</v>
       </c>
       <c r="S25" t="n">
         <v>4</v>
@@ -3299,13 +3311,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136983411</t>
+          <t>https://artportalen.se/Sighting/136984362</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>136983686</v>
+        <v>136984465</v>
       </c>
       <c r="B26" t="n">
         <v>99361</v>
@@ -3335,7 +3347,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -3354,13 +3366,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>579197</v>
+        <v>579207</v>
       </c>
       <c r="R26" t="n">
-        <v>6336710</v>
+        <v>6336640</v>
       </c>
       <c r="S26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3415,13 +3427,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136983686</t>
+          <t>https://artportalen.se/Sighting/136984465</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>136984362</v>
+        <v>136984524</v>
       </c>
       <c r="B27" t="n">
         <v>99361</v>
@@ -3451,7 +3463,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -3461,7 +3473,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3470,13 +3482,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>579226</v>
+        <v>579216</v>
       </c>
       <c r="R27" t="n">
-        <v>6336679</v>
+        <v>6336629</v>
       </c>
       <c r="S27" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3531,13 +3543,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136984362</t>
+          <t>https://artportalen.se/Sighting/136984524</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>136984465</v>
+        <v>136984621</v>
       </c>
       <c r="B28" t="n">
         <v>99361</v>
@@ -3567,17 +3579,17 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3586,10 +3598,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>579207</v>
+        <v>579238</v>
       </c>
       <c r="R28" t="n">
-        <v>6336640</v>
+        <v>6336576</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3647,13 +3659,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136984465</t>
+          <t>https://artportalen.se/Sighting/136984621</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>136984524</v>
+        <v>136984780</v>
       </c>
       <c r="B29" t="n">
         <v>99361</v>
@@ -3683,7 +3695,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3702,13 +3714,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>579216</v>
+        <v>579229</v>
       </c>
       <c r="R29" t="n">
-        <v>6336629</v>
+        <v>6336554</v>
       </c>
       <c r="S29" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3763,13 +3775,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136984524</t>
+          <t>https://artportalen.se/Sighting/136984780</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>136984621</v>
+        <v>136986187</v>
       </c>
       <c r="B30" t="n">
         <v>99361</v>
@@ -3799,17 +3811,12 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>överblommad</t>
+          <t>fullt utvecklade blad</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3818,13 +3825,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>579238</v>
+        <v>579345</v>
       </c>
       <c r="R30" t="n">
-        <v>6336576</v>
+        <v>6336499</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3879,13 +3886,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136984621</t>
+          <t>https://artportalen.se/Sighting/136986187</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>136984780</v>
+        <v>136988419</v>
       </c>
       <c r="B31" t="n">
         <v>99361</v>
@@ -3915,7 +3922,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3934,13 +3941,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>579229</v>
+        <v>579285</v>
       </c>
       <c r="R31" t="n">
-        <v>6336554</v>
+        <v>6336609</v>
       </c>
       <c r="S31" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3995,13 +4002,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136984780</t>
+          <t>https://artportalen.se/Sighting/136988419</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>136986187</v>
+        <v>136988674</v>
       </c>
       <c r="B32" t="n">
         <v>99361</v>
@@ -4031,12 +4038,17 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>fullt utvecklade blad</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4045,13 +4057,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>579345</v>
+        <v>579278</v>
       </c>
       <c r="R32" t="n">
-        <v>6336499</v>
+        <v>6336579</v>
       </c>
       <c r="S32" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4106,13 +4118,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136986187</t>
+          <t>https://artportalen.se/Sighting/136988674</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>136988419</v>
+        <v>136993796</v>
       </c>
       <c r="B33" t="n">
         <v>99361</v>
@@ -4142,32 +4154,26 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Horvan, Horvan, Sm</t>
+          <t>mönsterås, Sm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>579285</v>
+        <v>579433</v>
       </c>
       <c r="R33" t="n">
-        <v>6336609</v>
+        <v>6336481</v>
       </c>
       <c r="S33" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4205,85 +4211,80 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136988419</t>
+          <t>https://artportalen.se/Sighting/136993796</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>136988674</v>
+        <v>136993906</v>
       </c>
       <c r="B34" t="n">
-        <v>99361</v>
+        <v>106502</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Horvan, Horvan, Sm</t>
+          <t>MÖNSTERÅS, Sm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>579278</v>
+        <v>579189</v>
       </c>
       <c r="R34" t="n">
-        <v>6336579</v>
+        <v>6336730</v>
       </c>
       <c r="S34" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4321,60 +4322,61 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Lars Engström</t>
+          <t>Gunilla Rosendahl</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136988674</t>
+          <t>https://artportalen.se/Sighting/136993906</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>136993796</v>
+        <v>136993294</v>
       </c>
       <c r="B35" t="n">
-        <v>99361</v>
+        <v>98223</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J35" t="inlineStr"/>
@@ -4387,10 +4389,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>579433</v>
+        <v>579349</v>
       </c>
       <c r="R35" t="n">
-        <v>6336481</v>
+        <v>6336590</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4448,228 +4450,6 @@
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136993796</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>136993906</v>
-      </c>
-      <c r="B36" t="n">
-        <v>106502</v>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E36" t="n">
-        <v>221144</v>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Grönpyrola</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Pyrola chlorantha</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="N36" t="inlineStr"/>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>MÖNSTERÅS, Sm</t>
-        </is>
-      </c>
-      <c r="Q36" t="n">
-        <v>579189</v>
-      </c>
-      <c r="R36" t="n">
-        <v>6336730</v>
-      </c>
-      <c r="S36" t="n">
-        <v>1</v>
-      </c>
-      <c r="T36" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="V36" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W36" t="inlineStr">
-        <is>
-          <t>Fliseryd</t>
-        </is>
-      </c>
-      <c r="Y36" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AA36" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AD36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF36" t="inlineStr"/>
-      <c r="AG36" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT36" t="inlineStr"/>
-      <c r="AW36" t="inlineStr">
-        <is>
-          <t>Gunilla Rosendahl</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>Gunilla Rosendahl</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr"/>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/136993906</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>136993294</v>
-      </c>
-      <c r="B37" t="n">
-        <v>98223</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E37" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>mönsterås, Sm</t>
-        </is>
-      </c>
-      <c r="Q37" t="n">
-        <v>579349</v>
-      </c>
-      <c r="R37" t="n">
-        <v>6336590</v>
-      </c>
-      <c r="S37" t="n">
-        <v>1</v>
-      </c>
-      <c r="T37" t="inlineStr">
-        <is>
-          <t>Kalmar</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
-        <is>
-          <t>Mönsterås</t>
-        </is>
-      </c>
-      <c r="V37" t="inlineStr">
-        <is>
-          <t>Småland</t>
-        </is>
-      </c>
-      <c r="W37" t="inlineStr">
-        <is>
-          <t>Fliseryd</t>
-        </is>
-      </c>
-      <c r="Y37" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AA37" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="AD37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF37" t="inlineStr"/>
-      <c r="AG37" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT37" t="inlineStr"/>
-      <c r="AW37" t="inlineStr">
-        <is>
-          <t>Gunilla Rosendahl</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>Gunilla Rosendahl</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr"/>
-      <c r="AZ37" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/136993294</t>
         </is>
@@ -4711,8 +4491,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137059663</v>
       </c>
       <c r="B2" t="n">
-        <v>92753</v>
+        <v>92754</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137062062</v>
       </c>
       <c r="B3" t="n">
-        <v>92753</v>
+        <v>92754</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136988037</v>
       </c>
       <c r="B4" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136988735</v>
       </c>
       <c r="B5" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136993560</v>
       </c>
       <c r="B6" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136993864</v>
       </c>
       <c r="B7" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>137058412</v>
       </c>
       <c r="B8" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137060105</v>
       </c>
       <c r="B9" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>137060188</v>
       </c>
       <c r="B10" t="n">
-        <v>96946</v>
+        <v>96947</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136985036</v>
       </c>
       <c r="B11" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>136993200</v>
       </c>
       <c r="B12" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>136993642</v>
       </c>
       <c r="B13" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>137059377</v>
       </c>
       <c r="B14" t="n">
-        <v>92138</v>
+        <v>92139</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136987247</v>
       </c>
       <c r="B15" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137060719</v>
       </c>
       <c r="B16" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136986828</v>
       </c>
       <c r="B17" t="n">
-        <v>92795</v>
+        <v>92796</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>136988310</v>
       </c>
       <c r="B18" t="n">
-        <v>92795</v>
+        <v>92796</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>136983277</v>
       </c>
       <c r="B21" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>136983311</v>
       </c>
       <c r="B22" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>136983411</v>
       </c>
       <c r="B23" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>136983686</v>
       </c>
       <c r="B24" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>136984362</v>
       </c>
       <c r="B25" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>136984465</v>
       </c>
       <c r="B26" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>136984524</v>
       </c>
       <c r="B27" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>136984621</v>
       </c>
       <c r="B28" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>136984780</v>
       </c>
       <c r="B29" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136986187</v>
       </c>
       <c r="B30" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>136988419</v>
       </c>
       <c r="B31" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>136988674</v>
       </c>
       <c r="B32" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>136993796</v>
       </c>
       <c r="B33" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>136993906</v>
       </c>
       <c r="B34" t="n">
-        <v>106502</v>
+        <v>106503</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>136993294</v>
       </c>
       <c r="B35" t="n">
-        <v>98223</v>
+        <v>98224</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137059663</v>
       </c>
       <c r="B2" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137062062</v>
       </c>
       <c r="B3" t="n">
-        <v>92754</v>
+        <v>92760</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136988037</v>
       </c>
       <c r="B4" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136988735</v>
       </c>
       <c r="B5" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136993560</v>
       </c>
       <c r="B6" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136993864</v>
       </c>
       <c r="B7" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>137058412</v>
       </c>
       <c r="B8" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137060105</v>
       </c>
       <c r="B9" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>137060188</v>
       </c>
       <c r="B10" t="n">
-        <v>96947</v>
+        <v>96953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136985036</v>
       </c>
       <c r="B11" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>136993200</v>
       </c>
       <c r="B12" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>136993642</v>
       </c>
       <c r="B13" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>137059377</v>
       </c>
       <c r="B14" t="n">
-        <v>92139</v>
+        <v>92145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136987247</v>
       </c>
       <c r="B15" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137060719</v>
       </c>
       <c r="B16" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136986828</v>
       </c>
       <c r="B17" t="n">
-        <v>92796</v>
+        <v>92802</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>136988310</v>
       </c>
       <c r="B18" t="n">
-        <v>92796</v>
+        <v>92802</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>136983277</v>
       </c>
       <c r="B21" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>136983311</v>
       </c>
       <c r="B22" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>136983411</v>
       </c>
       <c r="B23" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>136983686</v>
       </c>
       <c r="B24" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>136984362</v>
       </c>
       <c r="B25" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>136984465</v>
       </c>
       <c r="B26" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>136984524</v>
       </c>
       <c r="B27" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>136984621</v>
       </c>
       <c r="B28" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>136984780</v>
       </c>
       <c r="B29" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136986187</v>
       </c>
       <c r="B30" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>136988419</v>
       </c>
       <c r="B31" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>136988674</v>
       </c>
       <c r="B32" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>136993796</v>
       </c>
       <c r="B33" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>136993906</v>
       </c>
       <c r="B34" t="n">
-        <v>106503</v>
+        <v>106509</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>136993294</v>
       </c>
       <c r="B35" t="n">
-        <v>98224</v>
+        <v>98230</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137059663</v>
       </c>
       <c r="B2" t="n">
-        <v>92760</v>
+        <v>92764</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137062062</v>
       </c>
       <c r="B3" t="n">
-        <v>92760</v>
+        <v>92764</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136988037</v>
       </c>
       <c r="B4" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136988735</v>
       </c>
       <c r="B5" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136993560</v>
       </c>
       <c r="B6" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136993864</v>
       </c>
       <c r="B7" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>137058412</v>
       </c>
       <c r="B8" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137060105</v>
       </c>
       <c r="B9" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>137060188</v>
       </c>
       <c r="B10" t="n">
-        <v>96953</v>
+        <v>96957</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136985036</v>
       </c>
       <c r="B11" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>136993200</v>
       </c>
       <c r="B12" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>136993642</v>
       </c>
       <c r="B13" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>137059377</v>
       </c>
       <c r="B14" t="n">
-        <v>92145</v>
+        <v>92149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136987247</v>
       </c>
       <c r="B15" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137060719</v>
       </c>
       <c r="B16" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136986828</v>
       </c>
       <c r="B17" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>136988310</v>
       </c>
       <c r="B18" t="n">
-        <v>92802</v>
+        <v>92806</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>136983277</v>
       </c>
       <c r="B21" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>136983311</v>
       </c>
       <c r="B22" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>136983411</v>
       </c>
       <c r="B23" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>136983686</v>
       </c>
       <c r="B24" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>136984362</v>
       </c>
       <c r="B25" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>136984465</v>
       </c>
       <c r="B26" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>136984524</v>
       </c>
       <c r="B27" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>136984621</v>
       </c>
       <c r="B28" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>136984780</v>
       </c>
       <c r="B29" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136986187</v>
       </c>
       <c r="B30" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>136988419</v>
       </c>
       <c r="B31" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>136988674</v>
       </c>
       <c r="B32" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>136993796</v>
       </c>
       <c r="B33" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>136993906</v>
       </c>
       <c r="B34" t="n">
-        <v>106509</v>
+        <v>106513</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>136993294</v>
       </c>
       <c r="B35" t="n">
-        <v>98230</v>
+        <v>98234</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136988037</v>
       </c>
       <c r="B4" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136988735</v>
       </c>
       <c r="B5" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136993560</v>
       </c>
       <c r="B6" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136993864</v>
       </c>
       <c r="B7" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>137058412</v>
       </c>
       <c r="B8" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137060105</v>
       </c>
       <c r="B9" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>137060188</v>
       </c>
       <c r="B10" t="n">
-        <v>96957</v>
+        <v>96959</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>136983277</v>
       </c>
       <c r="B21" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>136983311</v>
       </c>
       <c r="B22" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>136983411</v>
       </c>
       <c r="B23" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>136983686</v>
       </c>
       <c r="B24" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>136984362</v>
       </c>
       <c r="B25" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>136984465</v>
       </c>
       <c r="B26" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>136984524</v>
       </c>
       <c r="B27" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>136984621</v>
       </c>
       <c r="B28" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>136984780</v>
       </c>
       <c r="B29" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136986187</v>
       </c>
       <c r="B30" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>136988419</v>
       </c>
       <c r="B31" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>136988674</v>
       </c>
       <c r="B32" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>136993796</v>
       </c>
       <c r="B33" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>136993906</v>
       </c>
       <c r="B34" t="n">
-        <v>106513</v>
+        <v>106515</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>136993294</v>
       </c>
       <c r="B35" t="n">
-        <v>98234</v>
+        <v>98236</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137059663</v>
       </c>
       <c r="B2" t="n">
-        <v>92764</v>
+        <v>92766</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137062062</v>
       </c>
       <c r="B3" t="n">
-        <v>92764</v>
+        <v>92766</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136988037</v>
       </c>
       <c r="B4" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136988735</v>
       </c>
       <c r="B5" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136993560</v>
       </c>
       <c r="B6" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136993864</v>
       </c>
       <c r="B7" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>137058412</v>
       </c>
       <c r="B8" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137060105</v>
       </c>
       <c r="B9" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>137060188</v>
       </c>
       <c r="B10" t="n">
-        <v>96959</v>
+        <v>96961</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136985036</v>
       </c>
       <c r="B11" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>136993200</v>
       </c>
       <c r="B12" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>136993642</v>
       </c>
       <c r="B13" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>137059377</v>
       </c>
       <c r="B14" t="n">
-        <v>92149</v>
+        <v>92151</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136987247</v>
       </c>
       <c r="B15" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137060719</v>
       </c>
       <c r="B16" t="n">
-        <v>93464</v>
+        <v>93466</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136986828</v>
       </c>
       <c r="B17" t="n">
-        <v>92806</v>
+        <v>92808</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>136988310</v>
       </c>
       <c r="B18" t="n">
-        <v>92806</v>
+        <v>92808</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>136983277</v>
       </c>
       <c r="B21" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>136983311</v>
       </c>
       <c r="B22" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>136983411</v>
       </c>
       <c r="B23" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>136983686</v>
       </c>
       <c r="B24" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>136984362</v>
       </c>
       <c r="B25" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>136984465</v>
       </c>
       <c r="B26" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>136984524</v>
       </c>
       <c r="B27" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>136984621</v>
       </c>
       <c r="B28" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>136984780</v>
       </c>
       <c r="B29" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136986187</v>
       </c>
       <c r="B30" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>136988419</v>
       </c>
       <c r="B31" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>136988674</v>
       </c>
       <c r="B32" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>136993796</v>
       </c>
       <c r="B33" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>136993906</v>
       </c>
       <c r="B34" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>136993294</v>
       </c>
       <c r="B35" t="n">
-        <v>98236</v>
+        <v>98238</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137059663</v>
       </c>
       <c r="B2" t="n">
-        <v>92766</v>
+        <v>92779</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137062062</v>
       </c>
       <c r="B3" t="n">
-        <v>92766</v>
+        <v>92779</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136988037</v>
       </c>
       <c r="B4" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136988735</v>
       </c>
       <c r="B5" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136993560</v>
       </c>
       <c r="B6" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136993864</v>
       </c>
       <c r="B7" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>137058412</v>
       </c>
       <c r="B8" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137060105</v>
       </c>
       <c r="B9" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>137060188</v>
       </c>
       <c r="B10" t="n">
-        <v>96961</v>
+        <v>96974</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136985036</v>
       </c>
       <c r="B11" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>136993200</v>
       </c>
       <c r="B12" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>136993642</v>
       </c>
       <c r="B13" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>137059377</v>
       </c>
       <c r="B14" t="n">
-        <v>92151</v>
+        <v>92164</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136987247</v>
       </c>
       <c r="B15" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137060719</v>
       </c>
       <c r="B16" t="n">
-        <v>93466</v>
+        <v>93479</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136986828</v>
       </c>
       <c r="B17" t="n">
-        <v>92808</v>
+        <v>92821</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>136988310</v>
       </c>
       <c r="B18" t="n">
-        <v>92808</v>
+        <v>92821</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>137058966</v>
       </c>
       <c r="B19" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>137058799</v>
       </c>
       <c r="B20" t="n">
-        <v>58164</v>
+        <v>58177</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>136983277</v>
       </c>
       <c r="B21" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>136983311</v>
       </c>
       <c r="B22" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>136983411</v>
       </c>
       <c r="B23" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>136983686</v>
       </c>
       <c r="B24" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>136984362</v>
       </c>
       <c r="B25" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>136984465</v>
       </c>
       <c r="B26" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>136984524</v>
       </c>
       <c r="B27" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>136984621</v>
       </c>
       <c r="B28" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>136984780</v>
       </c>
       <c r="B29" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136986187</v>
       </c>
       <c r="B30" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>136988419</v>
       </c>
       <c r="B31" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>136988674</v>
       </c>
       <c r="B32" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>136993796</v>
       </c>
       <c r="B33" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>136993906</v>
       </c>
       <c r="B34" t="n">
-        <v>106517</v>
+        <v>106530</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>136993294</v>
       </c>
       <c r="B35" t="n">
-        <v>98238</v>
+        <v>98251</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137059663</v>
       </c>
       <c r="B2" t="n">
-        <v>92779</v>
+        <v>92781</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137062062</v>
       </c>
       <c r="B3" t="n">
-        <v>92779</v>
+        <v>92781</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136988037</v>
       </c>
       <c r="B4" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136988735</v>
       </c>
       <c r="B5" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136993560</v>
       </c>
       <c r="B6" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136993864</v>
       </c>
       <c r="B7" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>137058412</v>
       </c>
       <c r="B8" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137060105</v>
       </c>
       <c r="B9" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>137060188</v>
       </c>
       <c r="B10" t="n">
-        <v>96974</v>
+        <v>96976</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136985036</v>
       </c>
       <c r="B11" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>136993200</v>
       </c>
       <c r="B12" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>136993642</v>
       </c>
       <c r="B13" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>137059377</v>
       </c>
       <c r="B14" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136987247</v>
       </c>
       <c r="B15" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137060719</v>
       </c>
       <c r="B16" t="n">
-        <v>93479</v>
+        <v>93480</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136986828</v>
       </c>
       <c r="B17" t="n">
-        <v>92821</v>
+        <v>92823</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>136988310</v>
       </c>
       <c r="B18" t="n">
-        <v>92821</v>
+        <v>92823</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>137058966</v>
       </c>
       <c r="B19" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
         <v>137058799</v>
       </c>
       <c r="B20" t="n">
-        <v>58177</v>
+        <v>58179</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>136983277</v>
       </c>
       <c r="B21" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2856,7 +2856,7 @@
         <v>136983311</v>
       </c>
       <c r="B22" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2972,7 +2972,7 @@
         <v>136983411</v>
       </c>
       <c r="B23" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3088,7 +3088,7 @@
         <v>136983686</v>
       </c>
       <c r="B24" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3204,7 +3204,7 @@
         <v>136984362</v>
       </c>
       <c r="B25" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3320,7 +3320,7 @@
         <v>136984465</v>
       </c>
       <c r="B26" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
         <v>136984524</v>
       </c>
       <c r="B27" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>136984621</v>
       </c>
       <c r="B28" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3668,7 +3668,7 @@
         <v>136984780</v>
       </c>
       <c r="B29" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3784,7 +3784,7 @@
         <v>136986187</v>
       </c>
       <c r="B30" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3895,7 +3895,7 @@
         <v>136988419</v>
       </c>
       <c r="B31" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4011,7 +4011,7 @@
         <v>136988674</v>
       </c>
       <c r="B32" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4127,7 +4127,7 @@
         <v>136993796</v>
       </c>
       <c r="B33" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4238,7 +4238,7 @@
         <v>136993906</v>
       </c>
       <c r="B34" t="n">
-        <v>106530</v>
+        <v>106532</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4349,7 +4349,7 @@
         <v>136993294</v>
       </c>
       <c r="B35" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -2557,11 +2557,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
+      <c r="M19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Horvan, Horvan, Sm</t>
@@ -2775,11 +2771,7 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Horvan, Horvan, Sm</t>
@@ -2891,11 +2883,7 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Horvan, Horvan, Sm</t>
@@ -3007,11 +2995,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Horvan, Horvan, Sm</t>
@@ -3123,11 +3107,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Horvan, Horvan, Sm</t>
@@ -3239,11 +3219,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Horvan, Horvan, Sm</t>
@@ -3355,11 +3331,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Horvan, Horvan, Sm</t>
@@ -3471,11 +3443,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Horvan, Horvan, Sm</t>
@@ -3587,11 +3555,7 @@
           <t>stjälkar/strån/skott</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Horvan, Horvan, Sm</t>
@@ -3703,11 +3667,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Horvan, Horvan, Sm</t>
@@ -3814,11 +3774,7 @@
           <t>2</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Horvan, Horvan, Sm</t>
@@ -3930,11 +3886,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Horvan, Horvan, Sm</t>
@@ -4046,11 +3998,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Horvan, Horvan, Sm</t>

--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137059663</v>
       </c>
       <c r="B2" t="n">
-        <v>92781</v>
+        <v>92784</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137062062</v>
       </c>
       <c r="B3" t="n">
-        <v>92781</v>
+        <v>92784</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136988037</v>
       </c>
       <c r="B4" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136988735</v>
       </c>
       <c r="B5" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136993560</v>
       </c>
       <c r="B6" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136993864</v>
       </c>
       <c r="B7" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>137058412</v>
       </c>
       <c r="B8" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137060105</v>
       </c>
       <c r="B9" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>137060188</v>
       </c>
       <c r="B10" t="n">
-        <v>96976</v>
+        <v>96979</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136985036</v>
       </c>
       <c r="B11" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>136993200</v>
       </c>
       <c r="B12" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>136993642</v>
       </c>
       <c r="B13" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>137059377</v>
       </c>
       <c r="B14" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136987247</v>
       </c>
       <c r="B15" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137060719</v>
       </c>
       <c r="B16" t="n">
-        <v>93480</v>
+        <v>93483</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136986828</v>
       </c>
       <c r="B17" t="n">
-        <v>92823</v>
+        <v>92826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>136988310</v>
       </c>
       <c r="B18" t="n">
-        <v>92823</v>
+        <v>92826</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>136983277</v>
       </c>
       <c r="B21" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>136983311</v>
       </c>
       <c r="B22" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>136983411</v>
       </c>
       <c r="B23" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136983686</v>
       </c>
       <c r="B24" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>136984362</v>
       </c>
       <c r="B25" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>136984465</v>
       </c>
       <c r="B26" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136984524</v>
       </c>
       <c r="B27" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>136984621</v>
       </c>
       <c r="B28" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>136984780</v>
       </c>
       <c r="B29" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136986187</v>
       </c>
       <c r="B30" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>136988419</v>
       </c>
       <c r="B31" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>136988674</v>
       </c>
       <c r="B32" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>136993796</v>
       </c>
       <c r="B33" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>136993906</v>
       </c>
       <c r="B34" t="n">
-        <v>106532</v>
+        <v>106536</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>136993294</v>
       </c>
       <c r="B35" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137059663</v>
       </c>
       <c r="B2" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137062062</v>
       </c>
       <c r="B3" t="n">
-        <v>92784</v>
+        <v>92794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136988037</v>
       </c>
       <c r="B4" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136988735</v>
       </c>
       <c r="B5" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136993560</v>
       </c>
       <c r="B6" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136993864</v>
       </c>
       <c r="B7" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>137058412</v>
       </c>
       <c r="B8" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137060105</v>
       </c>
       <c r="B9" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>137060188</v>
       </c>
       <c r="B10" t="n">
-        <v>96979</v>
+        <v>96989</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136985036</v>
       </c>
       <c r="B11" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>136993200</v>
       </c>
       <c r="B12" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>136993642</v>
       </c>
       <c r="B13" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>137059377</v>
       </c>
       <c r="B14" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136987247</v>
       </c>
       <c r="B15" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137060719</v>
       </c>
       <c r="B16" t="n">
-        <v>93483</v>
+        <v>93493</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136986828</v>
       </c>
       <c r="B17" t="n">
-        <v>92826</v>
+        <v>92836</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>136988310</v>
       </c>
       <c r="B18" t="n">
-        <v>92826</v>
+        <v>92836</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>137058966</v>
       </c>
       <c r="B19" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>137058799</v>
       </c>
       <c r="B20" t="n">
-        <v>58179</v>
+        <v>58189</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>136983277</v>
       </c>
       <c r="B21" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>136983311</v>
       </c>
       <c r="B22" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>136983411</v>
       </c>
       <c r="B23" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136983686</v>
       </c>
       <c r="B24" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>136984362</v>
       </c>
       <c r="B25" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>136984465</v>
       </c>
       <c r="B26" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136984524</v>
       </c>
       <c r="B27" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>136984621</v>
       </c>
       <c r="B28" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>136984780</v>
       </c>
       <c r="B29" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136986187</v>
       </c>
       <c r="B30" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>136988419</v>
       </c>
       <c r="B31" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>136988674</v>
       </c>
       <c r="B32" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>136993796</v>
       </c>
       <c r="B33" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>136993906</v>
       </c>
       <c r="B34" t="n">
-        <v>106536</v>
+        <v>106556</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>136993294</v>
       </c>
       <c r="B35" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137059663</v>
       </c>
       <c r="B2" t="n">
-        <v>92794</v>
+        <v>92795</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137062062</v>
       </c>
       <c r="B3" t="n">
-        <v>92794</v>
+        <v>92795</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136988037</v>
       </c>
       <c r="B4" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136988735</v>
       </c>
       <c r="B5" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136993560</v>
       </c>
       <c r="B6" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136993864</v>
       </c>
       <c r="B7" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>137058412</v>
       </c>
       <c r="B8" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137060105</v>
       </c>
       <c r="B9" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>137060188</v>
       </c>
       <c r="B10" t="n">
-        <v>96989</v>
+        <v>96990</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136985036</v>
       </c>
       <c r="B11" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>136993200</v>
       </c>
       <c r="B12" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>136993642</v>
       </c>
       <c r="B13" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>137059377</v>
       </c>
       <c r="B14" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136987247</v>
       </c>
       <c r="B15" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137060719</v>
       </c>
       <c r="B16" t="n">
-        <v>93493</v>
+        <v>93494</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136986828</v>
       </c>
       <c r="B17" t="n">
-        <v>92836</v>
+        <v>92837</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>136988310</v>
       </c>
       <c r="B18" t="n">
-        <v>92836</v>
+        <v>92837</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>136983277</v>
       </c>
       <c r="B21" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>136983311</v>
       </c>
       <c r="B22" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>136983411</v>
       </c>
       <c r="B23" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136983686</v>
       </c>
       <c r="B24" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>136984362</v>
       </c>
       <c r="B25" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>136984465</v>
       </c>
       <c r="B26" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136984524</v>
       </c>
       <c r="B27" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>136984621</v>
       </c>
       <c r="B28" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>136984780</v>
       </c>
       <c r="B29" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136986187</v>
       </c>
       <c r="B30" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>136988419</v>
       </c>
       <c r="B31" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>136988674</v>
       </c>
       <c r="B32" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>136993796</v>
       </c>
       <c r="B33" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>136993906</v>
       </c>
       <c r="B34" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>136993294</v>
       </c>
       <c r="B35" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137059663</v>
       </c>
       <c r="B2" t="n">
-        <v>92795</v>
+        <v>92798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137062062</v>
       </c>
       <c r="B3" t="n">
-        <v>92795</v>
+        <v>92798</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136988037</v>
       </c>
       <c r="B4" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136988735</v>
       </c>
       <c r="B5" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136993560</v>
       </c>
       <c r="B6" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136993864</v>
       </c>
       <c r="B7" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>137058412</v>
       </c>
       <c r="B8" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137060105</v>
       </c>
       <c r="B9" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>137060188</v>
       </c>
       <c r="B10" t="n">
-        <v>96990</v>
+        <v>96995</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136985036</v>
       </c>
       <c r="B11" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>136993200</v>
       </c>
       <c r="B12" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>136993642</v>
       </c>
       <c r="B13" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>137059377</v>
       </c>
       <c r="B14" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136987247</v>
       </c>
       <c r="B15" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137060719</v>
       </c>
       <c r="B16" t="n">
-        <v>93494</v>
+        <v>93499</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136986828</v>
       </c>
       <c r="B17" t="n">
-        <v>92837</v>
+        <v>92840</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>136988310</v>
       </c>
       <c r="B18" t="n">
-        <v>92837</v>
+        <v>92840</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>137058966</v>
       </c>
       <c r="B19" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>137058799</v>
       </c>
       <c r="B20" t="n">
-        <v>58189</v>
+        <v>58190</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>136983277</v>
       </c>
       <c r="B21" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>136983311</v>
       </c>
       <c r="B22" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>136983411</v>
       </c>
       <c r="B23" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136983686</v>
       </c>
       <c r="B24" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>136984362</v>
       </c>
       <c r="B25" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>136984465</v>
       </c>
       <c r="B26" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136984524</v>
       </c>
       <c r="B27" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>136984621</v>
       </c>
       <c r="B28" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>136984780</v>
       </c>
       <c r="B29" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136986187</v>
       </c>
       <c r="B30" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>136988419</v>
       </c>
       <c r="B31" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>136988674</v>
       </c>
       <c r="B32" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>136993796</v>
       </c>
       <c r="B33" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>136993906</v>
       </c>
       <c r="B34" t="n">
-        <v>106557</v>
+        <v>106562</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>136993294</v>
       </c>
       <c r="B35" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137059663</v>
       </c>
       <c r="B2" t="n">
-        <v>92798</v>
+        <v>92800</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137062062</v>
       </c>
       <c r="B3" t="n">
-        <v>92798</v>
+        <v>92800</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136988037</v>
       </c>
       <c r="B4" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136988735</v>
       </c>
       <c r="B5" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136993560</v>
       </c>
       <c r="B6" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136993864</v>
       </c>
       <c r="B7" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>137058412</v>
       </c>
       <c r="B8" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137060105</v>
       </c>
       <c r="B9" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>137060188</v>
       </c>
       <c r="B10" t="n">
-        <v>96995</v>
+        <v>96997</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136985036</v>
       </c>
       <c r="B11" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>136993200</v>
       </c>
       <c r="B12" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>136993642</v>
       </c>
       <c r="B13" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>137059377</v>
       </c>
       <c r="B14" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136987247</v>
       </c>
       <c r="B15" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137060719</v>
       </c>
       <c r="B16" t="n">
-        <v>93499</v>
+        <v>93501</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136986828</v>
       </c>
       <c r="B17" t="n">
-        <v>92840</v>
+        <v>92842</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>136988310</v>
       </c>
       <c r="B18" t="n">
-        <v>92840</v>
+        <v>92842</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>136983277</v>
       </c>
       <c r="B21" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>136983311</v>
       </c>
       <c r="B22" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>136983411</v>
       </c>
       <c r="B23" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136983686</v>
       </c>
       <c r="B24" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>136984362</v>
       </c>
       <c r="B25" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>136984465</v>
       </c>
       <c r="B26" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136984524</v>
       </c>
       <c r="B27" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>136984621</v>
       </c>
       <c r="B28" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>136984780</v>
       </c>
       <c r="B29" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136986187</v>
       </c>
       <c r="B30" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>136988419</v>
       </c>
       <c r="B31" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>136988674</v>
       </c>
       <c r="B32" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>136993796</v>
       </c>
       <c r="B33" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>136993906</v>
       </c>
       <c r="B34" t="n">
-        <v>106562</v>
+        <v>106565</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>136993294</v>
       </c>
       <c r="B35" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137059663</v>
       </c>
       <c r="B2" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137062062</v>
       </c>
       <c r="B3" t="n">
-        <v>92800</v>
+        <v>92805</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136988037</v>
       </c>
       <c r="B4" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136988735</v>
       </c>
       <c r="B5" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136993560</v>
       </c>
       <c r="B6" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136993864</v>
       </c>
       <c r="B7" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>137058412</v>
       </c>
       <c r="B8" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137060105</v>
       </c>
       <c r="B9" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>137060188</v>
       </c>
       <c r="B10" t="n">
-        <v>96997</v>
+        <v>97003</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136985036</v>
       </c>
       <c r="B11" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>136993200</v>
       </c>
       <c r="B12" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>136993642</v>
       </c>
       <c r="B13" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>137059377</v>
       </c>
       <c r="B14" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136987247</v>
       </c>
       <c r="B15" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137060719</v>
       </c>
       <c r="B16" t="n">
-        <v>93501</v>
+        <v>93507</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136986828</v>
       </c>
       <c r="B17" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>136988310</v>
       </c>
       <c r="B18" t="n">
-        <v>92842</v>
+        <v>92847</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>137058966</v>
       </c>
       <c r="B19" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>137058799</v>
       </c>
       <c r="B20" t="n">
-        <v>58190</v>
+        <v>58191</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>136983277</v>
       </c>
       <c r="B21" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>136983311</v>
       </c>
       <c r="B22" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>136983411</v>
       </c>
       <c r="B23" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136983686</v>
       </c>
       <c r="B24" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>136984362</v>
       </c>
       <c r="B25" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>136984465</v>
       </c>
       <c r="B26" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136984524</v>
       </c>
       <c r="B27" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>136984621</v>
       </c>
       <c r="B28" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>136984780</v>
       </c>
       <c r="B29" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136986187</v>
       </c>
       <c r="B30" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>136988419</v>
       </c>
       <c r="B31" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>136988674</v>
       </c>
       <c r="B32" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>136993796</v>
       </c>
       <c r="B33" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>136993906</v>
       </c>
       <c r="B34" t="n">
-        <v>106565</v>
+        <v>106571</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>136993294</v>
       </c>
       <c r="B35" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -4186,7 +4186,7 @@
         <v>136993906</v>
       </c>
       <c r="B34" t="n">
-        <v>106571</v>
+        <v>106572</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137059663</v>
       </c>
       <c r="B2" t="n">
-        <v>92805</v>
+        <v>92817</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137062062</v>
       </c>
       <c r="B3" t="n">
-        <v>92805</v>
+        <v>92817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136988037</v>
       </c>
       <c r="B4" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136988735</v>
       </c>
       <c r="B5" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136993560</v>
       </c>
       <c r="B6" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136993864</v>
       </c>
       <c r="B7" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>137058412</v>
       </c>
       <c r="B8" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137060105</v>
       </c>
       <c r="B9" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>137060188</v>
       </c>
       <c r="B10" t="n">
-        <v>97003</v>
+        <v>97015</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136985036</v>
       </c>
       <c r="B11" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>136993200</v>
       </c>
       <c r="B12" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>136993642</v>
       </c>
       <c r="B13" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>137059377</v>
       </c>
       <c r="B14" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136987247</v>
       </c>
       <c r="B15" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137060719</v>
       </c>
       <c r="B16" t="n">
-        <v>93507</v>
+        <v>93519</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136986828</v>
       </c>
       <c r="B17" t="n">
-        <v>92847</v>
+        <v>92859</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>136988310</v>
       </c>
       <c r="B18" t="n">
-        <v>92847</v>
+        <v>92859</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>136983277</v>
       </c>
       <c r="B21" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>136983311</v>
       </c>
       <c r="B22" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>136983411</v>
       </c>
       <c r="B23" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136983686</v>
       </c>
       <c r="B24" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>136984362</v>
       </c>
       <c r="B25" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>136984465</v>
       </c>
       <c r="B26" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136984524</v>
       </c>
       <c r="B27" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>136984621</v>
       </c>
       <c r="B28" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>136984780</v>
       </c>
       <c r="B29" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136986187</v>
       </c>
       <c r="B30" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>136988419</v>
       </c>
       <c r="B31" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>136988674</v>
       </c>
       <c r="B32" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>136993796</v>
       </c>
       <c r="B33" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>136993906</v>
       </c>
       <c r="B34" t="n">
-        <v>106572</v>
+        <v>106584</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>136993294</v>
       </c>
       <c r="B35" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137059663</v>
       </c>
       <c r="B2" t="n">
-        <v>92817</v>
+        <v>92818</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137062062</v>
       </c>
       <c r="B3" t="n">
-        <v>92817</v>
+        <v>92818</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136988037</v>
       </c>
       <c r="B4" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136988735</v>
       </c>
       <c r="B5" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136993560</v>
       </c>
       <c r="B6" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136993864</v>
       </c>
       <c r="B7" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>137058412</v>
       </c>
       <c r="B8" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137060105</v>
       </c>
       <c r="B9" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>137060188</v>
       </c>
       <c r="B10" t="n">
-        <v>97015</v>
+        <v>97016</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136985036</v>
       </c>
       <c r="B11" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>136993200</v>
       </c>
       <c r="B12" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>136993642</v>
       </c>
       <c r="B13" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>137059377</v>
       </c>
       <c r="B14" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136987247</v>
       </c>
       <c r="B15" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137060719</v>
       </c>
       <c r="B16" t="n">
-        <v>93519</v>
+        <v>93520</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136986828</v>
       </c>
       <c r="B17" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>136988310</v>
       </c>
       <c r="B18" t="n">
-        <v>92859</v>
+        <v>92860</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>136983277</v>
       </c>
       <c r="B21" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>136983311</v>
       </c>
       <c r="B22" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>136983411</v>
       </c>
       <c r="B23" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136983686</v>
       </c>
       <c r="B24" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>136984362</v>
       </c>
       <c r="B25" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>136984465</v>
       </c>
       <c r="B26" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136984524</v>
       </c>
       <c r="B27" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>136984621</v>
       </c>
       <c r="B28" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>136984780</v>
       </c>
       <c r="B29" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136986187</v>
       </c>
       <c r="B30" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>136988419</v>
       </c>
       <c r="B31" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>136988674</v>
       </c>
       <c r="B32" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>136993796</v>
       </c>
       <c r="B33" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>136993906</v>
       </c>
       <c r="B34" t="n">
-        <v>106584</v>
+        <v>106585</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>136993294</v>
       </c>
       <c r="B35" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137059663</v>
       </c>
       <c r="B2" t="n">
-        <v>92818</v>
+        <v>92821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137062062</v>
       </c>
       <c r="B3" t="n">
-        <v>92818</v>
+        <v>92821</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136988037</v>
       </c>
       <c r="B4" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136988735</v>
       </c>
       <c r="B5" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136993560</v>
       </c>
       <c r="B6" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136993864</v>
       </c>
       <c r="B7" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>137058412</v>
       </c>
       <c r="B8" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137060105</v>
       </c>
       <c r="B9" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>137060188</v>
       </c>
       <c r="B10" t="n">
-        <v>97016</v>
+        <v>97019</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136985036</v>
       </c>
       <c r="B11" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>136993200</v>
       </c>
       <c r="B12" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>136993642</v>
       </c>
       <c r="B13" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>137059377</v>
       </c>
       <c r="B14" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136987247</v>
       </c>
       <c r="B15" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137060719</v>
       </c>
       <c r="B16" t="n">
-        <v>93520</v>
+        <v>93523</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136986828</v>
       </c>
       <c r="B17" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>136988310</v>
       </c>
       <c r="B18" t="n">
-        <v>92860</v>
+        <v>92863</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>136983277</v>
       </c>
       <c r="B21" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>136983311</v>
       </c>
       <c r="B22" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>136983411</v>
       </c>
       <c r="B23" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136983686</v>
       </c>
       <c r="B24" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>136984362</v>
       </c>
       <c r="B25" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>136984465</v>
       </c>
       <c r="B26" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136984524</v>
       </c>
       <c r="B27" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>136984621</v>
       </c>
       <c r="B28" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>136984780</v>
       </c>
       <c r="B29" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136986187</v>
       </c>
       <c r="B30" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>136988419</v>
       </c>
       <c r="B31" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>136988674</v>
       </c>
       <c r="B32" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>136993796</v>
       </c>
       <c r="B33" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>136993906</v>
       </c>
       <c r="B34" t="n">
-        <v>106585</v>
+        <v>106588</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>136993294</v>
       </c>
       <c r="B35" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -905,7 +905,7 @@
         <v>136988037</v>
       </c>
       <c r="B4" t="n">
-        <v>97019</v>
+        <v>97020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136988735</v>
       </c>
       <c r="B5" t="n">
-        <v>97019</v>
+        <v>97020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136993560</v>
       </c>
       <c r="B6" t="n">
-        <v>97019</v>
+        <v>97020</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136993864</v>
       </c>
       <c r="B7" t="n">
-        <v>97019</v>
+        <v>97020</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136985036</v>
       </c>
       <c r="B11" t="n">
-        <v>92206</v>
+        <v>92207</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>136993200</v>
       </c>
       <c r="B12" t="n">
-        <v>92206</v>
+        <v>92207</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>136993642</v>
       </c>
       <c r="B13" t="n">
-        <v>92206</v>
+        <v>92207</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136987247</v>
       </c>
       <c r="B15" t="n">
-        <v>93523</v>
+        <v>93524</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136986828</v>
       </c>
       <c r="B17" t="n">
-        <v>92863</v>
+        <v>92864</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>136988310</v>
       </c>
       <c r="B18" t="n">
-        <v>92863</v>
+        <v>92864</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>136983277</v>
       </c>
       <c r="B21" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>136983311</v>
       </c>
       <c r="B22" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>136983411</v>
       </c>
       <c r="B23" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136983686</v>
       </c>
       <c r="B24" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>136984362</v>
       </c>
       <c r="B25" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>136984465</v>
       </c>
       <c r="B26" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136984524</v>
       </c>
       <c r="B27" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>136984621</v>
       </c>
       <c r="B28" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>136984780</v>
       </c>
       <c r="B29" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136986187</v>
       </c>
       <c r="B30" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>136988419</v>
       </c>
       <c r="B31" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>136988674</v>
       </c>
       <c r="B32" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>136993796</v>
       </c>
       <c r="B33" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>136993906</v>
       </c>
       <c r="B34" t="n">
-        <v>106588</v>
+        <v>106590</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>136993294</v>
       </c>
       <c r="B35" t="n">
-        <v>98296</v>
+        <v>98297</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>

--- a/artfynd/A 29379-2026 artfynd.xlsx
+++ b/artfynd/A 29379-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137059663</v>
       </c>
       <c r="B2" t="n">
-        <v>92821</v>
+        <v>92825</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -794,7 +794,7 @@
         <v>137062062</v>
       </c>
       <c r="B3" t="n">
-        <v>92821</v>
+        <v>92825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>136988037</v>
       </c>
       <c r="B4" t="n">
-        <v>97020</v>
+        <v>97023</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>136988735</v>
       </c>
       <c r="B5" t="n">
-        <v>97020</v>
+        <v>97023</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1109,7 +1109,7 @@
         <v>136993560</v>
       </c>
       <c r="B6" t="n">
-        <v>97020</v>
+        <v>97023</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>136993864</v>
       </c>
       <c r="B7" t="n">
-        <v>97020</v>
+        <v>97023</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>137058412</v>
       </c>
       <c r="B8" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1433,7 +1433,7 @@
         <v>137060105</v>
       </c>
       <c r="B9" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1535,7 +1535,7 @@
         <v>137060188</v>
       </c>
       <c r="B10" t="n">
-        <v>97019</v>
+        <v>97023</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1646,7 +1646,7 @@
         <v>136985036</v>
       </c>
       <c r="B11" t="n">
-        <v>92207</v>
+        <v>92210</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1757,7 +1757,7 @@
         <v>136993200</v>
       </c>
       <c r="B12" t="n">
-        <v>92207</v>
+        <v>92210</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>136993642</v>
       </c>
       <c r="B13" t="n">
-        <v>92207</v>
+        <v>92210</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1977,7 +1977,7 @@
         <v>137059377</v>
       </c>
       <c r="B14" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2088,7 +2088,7 @@
         <v>136987247</v>
       </c>
       <c r="B15" t="n">
-        <v>93524</v>
+        <v>93527</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2199,7 +2199,7 @@
         <v>137060719</v>
       </c>
       <c r="B16" t="n">
-        <v>93523</v>
+        <v>93527</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2305,7 +2305,7 @@
         <v>136986828</v>
       </c>
       <c r="B17" t="n">
-        <v>92864</v>
+        <v>92867</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2416,7 +2416,7 @@
         <v>136988310</v>
       </c>
       <c r="B18" t="n">
-        <v>92864</v>
+        <v>92867</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2527,7 +2527,7 @@
         <v>137058966</v>
       </c>
       <c r="B19" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2634,7 +2634,7 @@
         <v>137058799</v>
       </c>
       <c r="B20" t="n">
-        <v>58191</v>
+        <v>58194</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2736,7 +2736,7 @@
         <v>136983277</v>
       </c>
       <c r="B21" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2848,7 +2848,7 @@
         <v>136983311</v>
       </c>
       <c r="B22" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2960,7 +2960,7 @@
         <v>136983411</v>
       </c>
       <c r="B23" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>136983686</v>
       </c>
       <c r="B24" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3184,7 +3184,7 @@
         <v>136984362</v>
       </c>
       <c r="B25" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3296,7 +3296,7 @@
         <v>136984465</v>
       </c>
       <c r="B26" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>136984524</v>
       </c>
       <c r="B27" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>136984621</v>
       </c>
       <c r="B28" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3632,7 +3632,7 @@
         <v>136984780</v>
       </c>
       <c r="B29" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136986187</v>
       </c>
       <c r="B30" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>136988419</v>
       </c>
       <c r="B31" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3963,7 +3963,7 @@
         <v>136988674</v>
       </c>
       <c r="B32" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4075,7 +4075,7 @@
         <v>136993796</v>
       </c>
       <c r="B33" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4186,7 +4186,7 @@
         <v>136993906</v>
       </c>
       <c r="B34" t="n">
-        <v>106590</v>
+        <v>106594</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>136993294</v>
       </c>
       <c r="B35" t="n">
-        <v>98297</v>
+        <v>98300</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
